--- a/technology.xlsx
+++ b/technology.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20416"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\hravoaha\Desktop\Thèse\Thèse 2023\Objectif 2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\hravoaha\Desktop\Thèse\Thèse 2023\Objectif 2\biowaste_optim\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C39EF5E-0A49-4AFC-A96B-19383D5CDB69}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36F419BD-B60B-4B07-945F-E1651FDB9AEA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6930" xr2:uid="{D746D7D5-B0A8-4858-AD5A-93AA09E65399}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6930" activeTab="4" xr2:uid="{D746D7D5-B0A8-4858-AD5A-93AA09E65399}"/>
   </bookViews>
   <sheets>
     <sheet name="id_tech" sheetId="2" r:id="rId1"/>
@@ -23,7 +23,7 @@
   <externalReferences>
     <externalReference r:id="rId7"/>
   </externalReferences>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>

--- a/technology.xlsx
+++ b/technology.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\hravoaha\Desktop\Thèse\Thèse 2023\Objectif 2\biowaste_optim\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36F419BD-B60B-4B07-945F-E1651FDB9AEA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9258860E-DCC3-4DCE-A847-E62CFA925527}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6930" activeTab="4" xr2:uid="{D746D7D5-B0A8-4858-AD5A-93AA09E65399}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6930" xr2:uid="{D746D7D5-B0A8-4858-AD5A-93AA09E65399}"/>
   </bookViews>
   <sheets>
     <sheet name="id_tech" sheetId="2" r:id="rId1"/>
